--- a/synoptic/output/Water chemistry table.xlsx
+++ b/synoptic/output/Water chemistry table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\Humedales Puerto Rico\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carla López Lloreda\Dropbox\Grad school\Research\Humedales Puerto Rico\PR-wetlands\synoptic\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BC80569-E489-45EC-9081-2EA247A13F4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BFCB559-AF4E-4CEB-9F96-343C4ED7BC00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{5FD0C9F6-0E44-44B6-A6D6-063BDD68D6CD}"/>
   </bookViews>
@@ -115,6 +115,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -149,10 +152,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,6 +495,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.77734375" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -868,35 +879,37 @@
       <c r="B12" t="s">
         <v>7</v>
       </c>
-      <c r="D12">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3">
         <f t="shared" ref="D12:L12" si="0">AVERAGE(D2:D4)</f>
         <v>464.9424207848694</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3">
         <f t="shared" si="0"/>
         <v>1.6042852070109541</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="3">
         <f t="shared" si="0"/>
         <v>3.0397639908372902</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="3">
         <f t="shared" si="0"/>
         <v>58.693500776350056</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="3">
         <f t="shared" si="0"/>
         <v>222.48119275973795</v>
       </c>
-      <c r="J12">
+      <c r="I12" s="3"/>
+      <c r="J12" s="3">
         <f t="shared" si="0"/>
         <v>7.8760193862590242</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="3">
         <f t="shared" si="0"/>
         <v>20.229602970086617</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="3">
         <f t="shared" si="0"/>
         <v>45.904984214210266</v>
       </c>
@@ -905,43 +918,43 @@
       <c r="B13" t="s">
         <v>8</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <f>AVERAGE(C5:C7)</f>
         <v>0.34070090635833999</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="3">
         <f t="shared" ref="D13:L13" si="1">AVERAGE(D5:D7)</f>
         <v>95.860237752497923</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="3">
         <f t="shared" si="1"/>
         <v>0.38345058068133714</v>
       </c>
-      <c r="F13">
-        <f t="shared" si="1"/>
+      <c r="F13" s="3">
+        <f>AVERAGE(F5:F7)</f>
         <v>2.6762552436526005E-2</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="3">
         <f t="shared" si="1"/>
         <v>0.80279973962198126</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="3">
         <f t="shared" si="1"/>
         <v>74.128736241138043</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="3">
         <f t="shared" si="1"/>
         <v>0.11180620743233333</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="3">
         <f t="shared" si="1"/>
         <v>3.1596182439816674</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="3">
         <f t="shared" si="1"/>
         <v>6.9564835061022938</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="3">
         <f t="shared" si="1"/>
         <v>32.99153569180222</v>
       </c>
@@ -950,35 +963,37 @@
       <c r="B14" t="s">
         <v>6</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="3">
         <f>AVERAGE(C8:C10)</f>
         <v>0.27235223483717225</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="3">
         <f t="shared" ref="D14:L14" si="2">AVERAGE(D8:D10)</f>
         <v>408.88252662308531</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="3">
         <f t="shared" si="2"/>
         <v>0.7956607752326722</v>
       </c>
-      <c r="G14">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3">
         <f t="shared" si="2"/>
         <v>19.709026127276072</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="3">
         <f t="shared" si="2"/>
         <v>160.87233479747269</v>
       </c>
-      <c r="J14">
+      <c r="I14" s="3"/>
+      <c r="J14" s="3">
         <f t="shared" si="2"/>
         <v>4.4447738215891759</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="3">
         <f t="shared" si="2"/>
         <v>12.930258901425832</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="3">
         <f t="shared" si="2"/>
         <v>91.70500096835616</v>
       </c>
@@ -989,7 +1004,7 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="C13:L13 D12:H12 J12:L12 C14:E14 J14:L14 G14:H14" evalError="1"/>
+    <ignoredError sqref="C13:E13 D12:H12 J12:L12 C14:E14 J14:L14 G14:H14 G13:L13" evalError="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
